--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/ILLINOIS_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/ILLINOIS_2018.xlsx
@@ -3793,7 +3793,7 @@
         <v>613</v>
       </c>
       <c r="D191">
-        <v>0.009044766429604273</v>
+        <v>0.009044766429604272</v>
       </c>
     </row>
     <row r="192">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C214">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C372">
@@ -11173,7 +11173,7 @@
         <v>64</v>
       </c>
       <c r="D601">
-        <v>0.0009443149290288311</v>
+        <v>0.0009443149290288312</v>
       </c>
     </row>
     <row r="602">
@@ -11533,7 +11533,7 @@
         <v>63</v>
       </c>
       <c r="D621">
-        <v>0.0009295600082627557</v>
+        <v>0.0009295600082627556</v>
       </c>
     </row>
     <row r="622">
@@ -12019,7 +12019,7 @@
         <v>63</v>
       </c>
       <c r="D648">
-        <v>0.0009295600082627557</v>
+        <v>0.0009295600082627556</v>
       </c>
     </row>
     <row r="649">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C849">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C850">
@@ -18420,7 +18420,7 @@
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1004">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1057">
@@ -19536,7 +19536,7 @@
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1066">
